--- a/research/traditional_assets/database/data/australia/australia_office_equipment_services.xlsx
+++ b/research/traditional_assets/database/data/australia/australia_office_equipment_services.xlsx
@@ -588,28 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0153</v>
-      </c>
-      <c r="E2">
-        <v>0.253</v>
+        <v>0.146</v>
       </c>
       <c r="G2">
-        <v>0.02964824120603015</v>
+        <v>-0.01879629629629629</v>
       </c>
       <c r="H2">
-        <v>-0.00263819095477387</v>
+        <v>-0.01981481481481481</v>
       </c>
       <c r="I2">
-        <v>-0.00464824120603015</v>
+        <v>-0.02592592592592593</v>
       </c>
       <c r="J2">
-        <v>-0.00464824120603015</v>
+        <v>-0.02592592592592593</v>
       </c>
       <c r="K2">
-        <v>0.19</v>
+        <v>-1.29</v>
       </c>
       <c r="L2">
-        <v>0.02386934673366834</v>
+        <v>-0.1194444444444444</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -618,7 +615,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -627,79 +624,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.608</v>
+        <v>0.63</v>
       </c>
       <c r="V2">
-        <v>0.1936305732484076</v>
+        <v>0.3480662983425414</v>
       </c>
       <c r="W2">
-        <v>-0.1862745098039216</v>
+        <v>-5.733333333333333</v>
       </c>
       <c r="X2">
-        <v>0.1692835832965324</v>
+        <v>0.1817518712728061</v>
       </c>
       <c r="Y2">
-        <v>-0.3555580931004539</v>
+        <v>-5.91508520460614</v>
       </c>
       <c r="Z2">
-        <v>3.398804440649017</v>
+        <v>3.079555175363559</v>
       </c>
       <c r="AA2">
-        <v>-0.01579846285226302</v>
+        <v>-0.07984031936127745</v>
       </c>
       <c r="AB2">
-        <v>0.07958483777947581</v>
+        <v>0.06292676466981187</v>
       </c>
       <c r="AC2">
-        <v>-0.09538330063173883</v>
+        <v>-0.1427670840310893</v>
       </c>
       <c r="AD2">
-        <v>7.33</v>
+        <v>7.87</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>7.33</v>
+        <v>7.87</v>
       </c>
       <c r="AG2">
-        <v>6.722</v>
+        <v>7.24</v>
       </c>
       <c r="AH2">
-        <v>0.7000955109837631</v>
+        <v>0.8130165289256198</v>
       </c>
       <c r="AI2">
-        <v>0.9215489062107116</v>
+        <v>1.122361665715915</v>
       </c>
       <c r="AJ2">
-        <v>0.6816061650780775</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="AK2">
-        <v>0.9150558126871767</v>
+        <v>1.134440614227515</v>
       </c>
       <c r="AL2">
-        <v>0.636</v>
+        <v>1.04</v>
       </c>
       <c r="AM2">
-        <v>0.635</v>
+        <v>1.038</v>
       </c>
       <c r="AN2">
-        <v>-349.047619047619</v>
+        <v>-36.77570093457944</v>
       </c>
       <c r="AO2">
-        <v>-0.05817610062893081</v>
+        <v>-0.2692307692307693</v>
       </c>
       <c r="AP2">
-        <v>-320.0952380952381</v>
+        <v>-33.83177570093458</v>
       </c>
       <c r="AQ2">
-        <v>-0.05826771653543307</v>
+        <v>-0.2697495183044316</v>
       </c>
     </row>
     <row r="3">
@@ -719,28 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0153</v>
-      </c>
-      <c r="E3">
-        <v>0.253</v>
+        <v>0.146</v>
       </c>
       <c r="G3">
-        <v>0.02964824120603015</v>
+        <v>-0.01879629629629629</v>
       </c>
       <c r="H3">
-        <v>-0.00263819095477387</v>
+        <v>-0.01981481481481481</v>
       </c>
       <c r="I3">
-        <v>-0.00464824120603015</v>
+        <v>-0.02592592592592593</v>
       </c>
       <c r="J3">
-        <v>-0.00464824120603015</v>
+        <v>-0.02592592592592593</v>
       </c>
       <c r="K3">
-        <v>0.19</v>
+        <v>-1.29</v>
       </c>
       <c r="L3">
-        <v>0.02386934673366834</v>
+        <v>-0.1194444444444444</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -749,7 +743,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -758,79 +752,79 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.608</v>
+        <v>0.63</v>
       </c>
       <c r="V3">
-        <v>0.1936305732484076</v>
+        <v>0.3480662983425414</v>
       </c>
       <c r="W3">
-        <v>-0.1862745098039216</v>
+        <v>-5.733333333333333</v>
       </c>
       <c r="X3">
-        <v>0.1692835832965324</v>
+        <v>0.1817518712728061</v>
       </c>
       <c r="Y3">
-        <v>-0.3555580931004539</v>
+        <v>-5.91508520460614</v>
       </c>
       <c r="Z3">
-        <v>3.398804440649017</v>
+        <v>3.079555175363559</v>
       </c>
       <c r="AA3">
-        <v>-0.01579846285226302</v>
+        <v>-0.07984031936127745</v>
       </c>
       <c r="AB3">
-        <v>0.07958483777947581</v>
+        <v>0.06292676466981187</v>
       </c>
       <c r="AC3">
-        <v>-0.09538330063173883</v>
+        <v>-0.1427670840310893</v>
       </c>
       <c r="AD3">
-        <v>7.33</v>
+        <v>7.87</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>7.33</v>
+        <v>7.87</v>
       </c>
       <c r="AG3">
-        <v>6.722</v>
+        <v>7.24</v>
       </c>
       <c r="AH3">
-        <v>0.7000955109837631</v>
+        <v>0.8130165289256198</v>
       </c>
       <c r="AI3">
-        <v>0.9215489062107116</v>
+        <v>1.122361665715915</v>
       </c>
       <c r="AJ3">
-        <v>0.6816061650780775</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="AK3">
-        <v>0.9150558126871767</v>
+        <v>1.134440614227515</v>
       </c>
       <c r="AL3">
-        <v>0.636</v>
+        <v>1.04</v>
       </c>
       <c r="AM3">
-        <v>0.635</v>
+        <v>1.038</v>
       </c>
       <c r="AN3">
-        <v>-349.047619047619</v>
+        <v>-36.77570093457944</v>
       </c>
       <c r="AO3">
-        <v>-0.05817610062893081</v>
+        <v>-0.2692307692307693</v>
       </c>
       <c r="AP3">
-        <v>-320.0952380952381</v>
+        <v>-33.83177570093458</v>
       </c>
       <c r="AQ3">
-        <v>-0.05826771653543307</v>
+        <v>-0.2697495183044316</v>
       </c>
     </row>
   </sheetData>
